--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA :: å°� ä¸ª</t>
+          <t>L18: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F, U+4E2A CJK UNIFIED IDEOGRAPH-4E2A :: 小 个</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To other members of the Profession,â€”to the country practi-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L32: isolated marker/symbol line :: X</t>
@@ -628,7 +632,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tioners, and to those who have not hitherto been much in this Court—</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +666,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: nave not hitherto been much in this Courtâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ tioners, and to those who have not hitherto been much in this Courtâ€”</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tioners, and to those who have not hitherto been much in this Court—</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -709,16 +713,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: date of our first Chancery Act â€” among the</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prior to March, 1837, the date of our first Chancery Actâ€”among the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -746,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -945,12 +941,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +985,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1106,7 +1102,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
